--- a/reports/pdf_change_20260826.xlsx
+++ b/reports/pdf_change_20260826.xlsx
@@ -38,11 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -67,6 +62,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,18 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 40억(0.9%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -588,273 +588,1099 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>하림지주</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>896594400</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.73%→0.92%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>287→365</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-4651274000</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>5.51%→4.55%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>366→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1251450000</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>0.52%→0.81%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>59→89</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-882637900</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.53%→0.30%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>170→103</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2238705000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>0.48%→0.98%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>9→18</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나  (편출)</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-541471000</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.12%→0.00%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>7→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>827296000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.83%→0.98%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>35→43</t>
+        </is>
+      </c>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="17" t="n"/>
     </row>
     <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 2억(0.6%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 1종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 19억(0.5%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 32억(1.2%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 6종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
+      <c r="K15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>아이티센글로벌  (신규)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>110</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>3127410000</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.21%</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>0→110</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-158</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-1497366000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>1.14%→0.55%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>308→150</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>5005891800</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>4.41%→6.67%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>149→210</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피  (편출)</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-910802880</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.00%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>144→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>1480096800</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>1.12%→1.64%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>39→60</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (편출)</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-116</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-706015440</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>116→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3495960000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>1.04%→2.37%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>15→35</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>메쥬  (편출)</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-709188480</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>0.28%→0.00%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>77→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>179599680</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>1.70%→1.94%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>350→363</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-738855000</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.65%→0.40%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>120→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3382236000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.31%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>0→12</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-2211791400</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>1.55%→0.70%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>89→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-1500735600</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>4.70%→4.13%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>341→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-7506135000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>7.49%→3.98%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>83→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 32억(1.4%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 3종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>2168156900</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>3.73%→4.71%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>339→430</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-69</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-4408768800</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>15.31%→13.26%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>520→451</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>4052088000</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>6.97%→8.47%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>85→109</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-2059070000</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>11.48%→10.23%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>236→216</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>26245560</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>0.77%→0.78%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>253→257</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>스피어</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B36" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C36" s="11" t="n">
         <v>44348200</v>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>2.30%→2.46%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>367→393</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>인텍플러스</t>
         </is>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H36" s="15" t="n">
         <v>-19</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I36" s="15" t="n">
         <v>-45976200</v>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>3.09%→2.93%</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>348→329</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="19" t="n"/>
-      <c r="B15" s="19" t="n"/>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="G15" s="16" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>새로닉스</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H37" s="15" t="n">
         <v>-18</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I37" s="15" t="n">
         <v>-16223760</v>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>2.90%→2.84%</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>876→858</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억   ·   현금 3억(0.6%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A18:K18"/>
+  <mergeCells count="19">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A12:K12"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="G34:K34"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260826.xlsx
+++ b/reports/pdf_change_20260826.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억   ·   현금 40억(0.9%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4651274000</v>
+        <v>-882637900</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>5.51%→4.55%</t>
+          <t>0.53%→0.30%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>366→299</t>
+          <t>170→103</t>
         </is>
       </c>
     </row>
@@ -728,23 +728,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-882637900</v>
+        <v>-4651274000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.53%→0.30%</t>
+          <t>5.51%→4.55%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>170→103</t>
+          <t>366→299</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억   ·   현금 19억(0.5%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -847,7 +847,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억   ·   현금 32억(1.2%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -1256,7 +1256,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억   ·   현금 32억(1.4%)      당일 2026-08-26  vs  전영업일 2026-08-25      매수 3종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>

--- a/reports/pdf_change_20260826.xlsx
+++ b/reports/pdf_change_20260826.xlsx
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-882637900</v>
+        <v>-4651274000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>0.53%→0.30%</t>
+          <t>5.51%→4.55%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>170→103</t>
+          <t>366→299</t>
         </is>
       </c>
     </row>
@@ -728,23 +728,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-4651274000</v>
+        <v>-882637900</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>5.51%→4.55%</t>
+          <t>0.53%→0.30%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>366→299</t>
+          <t>170→103</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260826.xlsx
+++ b/reports/pdf_change_20260826.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,456억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 4종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,588억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -823,7 +823,7 @@
     <row r="11" ht="19" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,915억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,836억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B11" s="4" t="n"/>
@@ -847,7 +847,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,521억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 6종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,606억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 6종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -943,7 +943,7 @@
         <v>110</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3127410000</v>
+        <v>3114045000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>-158</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1497366000</v>
+        <v>-1490967000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>61</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>5005891800</v>
+        <v>4984499100</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>-144</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-910802880</v>
+        <v>-906910560</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>21</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1480096800</v>
+        <v>1473771600</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>-116</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-706015440</v>
+        <v>-702998280</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>20</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3495960000</v>
+        <v>3481020000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>-77</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-709188480</v>
+        <v>-706157760</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>13</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>179599680</v>
+        <v>178832160</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>-50</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-738855000</v>
+        <v>-735697500</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3382236000</v>
+        <v>3367782000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>-49</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-2211791400</v>
+        <v>-2202339300</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>-42</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1500735600</v>
+        <v>-1494322200</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>-35</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-7506135000</v>
+        <v>-7474057500</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,255억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 3종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,218억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1352,7 +1352,7 @@
         <v>91</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2168156900</v>
+        <v>2174590600</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>-69</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-4408768800</v>
+        <v>-4421851200</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>24</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4052088000</v>
+        <v>4064112000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>-20</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-2059070000</v>
+        <v>-2065180000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>26245560</v>
+        <v>26323440</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 1종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1557,11 +1557,11 @@
         <v>26</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>44348200</v>
+        <v>45310200</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2.30%→2.46%</t>
+          <t>2.29%→2.45%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1578,11 +1578,11 @@
         <v>-19</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-45976200</v>
+        <v>-50334800</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>3.09%→2.93%</t>
+          <t>3.30%→3.12%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1606,11 +1606,11 @@
         <v>-18</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-16223760</v>
+        <v>-16383600</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.84%</t>
+          <t>2.86%→2.80%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1622,7 +1622,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 560억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 544억      당일 2026-08-26  vs  전영업일 2026-08-25      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>

--- a/reports/pdf_change_20260826.xlsx
+++ b/reports/pdf_change_20260826.xlsx
@@ -684,23 +684,23 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4651274000</v>
+        <v>-882637900</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>5.51%→4.55%</t>
+          <t>0.53%→0.30%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>366→299</t>
+          <t>170→103</t>
         </is>
       </c>
     </row>
@@ -728,23 +728,23 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
         <v>-67</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-882637900</v>
+        <v>-4651274000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.53%→0.30%</t>
+          <t>5.51%→4.55%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>170→103</t>
+          <t>366→299</t>
         </is>
       </c>
     </row>
